--- a/southern_europe/italy_data/geographical_feature/node_metrics_150.xlsx
+++ b/southern_europe/italy_data/geographical_feature/node_metrics_150.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0954659\PycharmProjects\AdOpT-NET0_luca\southern_europe\italy_data\geographical_feature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB0F524-E8F2-4AF6-98BC-7FD00EF4E63C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF9B387E-FE91-4830-B852-DFF31AAA8959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-6768" windowWidth="30936" windowHeight="16776" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nodes" sheetId="1" r:id="rId1"/>
@@ -158,9 +158,6 @@
   </si>
   <si>
     <t>TERMOVALORIZZAOTRE DI VERONA</t>
-  </si>
-  <si>
-    <t>HERAMBIENTE S.R.L.  - IMPIANTO DI TERMOVALORIZZAZIONE RIFIUTI NON PERICOLOSI</t>
   </si>
   <si>
     <t>TERMOVALORIZZATORE DI BOLZANO</t>
@@ -549,6 +546,9 @@
   <si>
     <t>Node type</t>
   </si>
+  <si>
+    <t>HERAMBIENTE S.R.L.  - Termovalorizzatore</t>
+  </si>
 </sst>
 </file>
 
@@ -667,7 +667,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -695,7 +695,6 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -915,7 +914,7 @@
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.5" customWidth="1"/>
-    <col min="2" max="2" width="39.5" customWidth="1"/>
+    <col min="2" max="2" width="107.296875" customWidth="1"/>
     <col min="3" max="4" width="10.796875" customWidth="1"/>
     <col min="5" max="5" width="10.5" customWidth="1"/>
     <col min="6" max="6" width="14.296875" customWidth="1"/>
@@ -1655,8 +1654,8 @@
       <c r="A29" s="4">
         <v>27</v>
       </c>
-      <c r="B29" s="17" t="s">
-        <v>38</v>
+      <c r="B29" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="C29" s="2">
         <v>10.943759999999999</v>
@@ -1682,7 +1681,7 @@
         <v>28</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30" s="2">
         <v>11.30925</v>
@@ -1708,7 +1707,7 @@
         <v>29</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" s="2">
         <v>11.556369999999999</v>
@@ -1734,7 +1733,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C32" s="2">
         <v>11.428890000000001</v>
@@ -1760,7 +1759,7 @@
         <v>31</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" s="2">
         <v>11.75079</v>
@@ -1786,7 +1785,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C34" s="5">
         <v>11.69642</v>
@@ -1812,7 +1811,7 @@
         <v>33</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C35" s="2">
         <v>11.963570000000001</v>
@@ -1838,7 +1837,7 @@
         <v>34</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C36" s="2">
         <v>11.924099999999999</v>
@@ -1864,7 +1863,7 @@
         <v>35</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="2">
         <v>12.08798</v>
@@ -1890,7 +1889,7 @@
         <v>36</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" s="2">
         <v>12.269209999999999</v>
@@ -1916,7 +1915,7 @@
         <v>37</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C39" s="2">
         <v>12.2</v>
@@ -1934,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1942,7 +1941,7 @@
         <v>38</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C40" s="5">
         <v>12.31551</v>
@@ -1968,7 +1967,7 @@
         <v>39</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C41" s="2">
         <v>12.74245</v>
@@ -1994,7 +1993,7 @@
         <v>40</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="2">
         <v>12.63189</v>
@@ -2020,7 +2019,7 @@
         <v>41</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C43" s="17">
         <v>13.80006</v>
@@ -2046,7 +2045,7 @@
         <v>42</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C44" s="17">
         <v>12.274480000000001</v>
@@ -2072,7 +2071,7 @@
         <v>43</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C45" s="17">
         <v>12.564</v>
@@ -2090,7 +2089,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -2098,7 +2097,7 @@
         <v>44</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C46" s="17">
         <v>10.64</v>
@@ -27384,45 +27383,45 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="C1" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="D1" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="12">
         <v>11.75079</v>
@@ -27437,25 +27436,25 @@
         <v>11</v>
       </c>
       <c r="F2" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>70</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>71</v>
       </c>
       <c r="I2" s="11">
         <v>800000</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K2" s="11">
         <v>2021</v>
       </c>
       <c r="L2" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M2" s="15"/>
       <c r="N2" s="15"/>
@@ -27474,7 +27473,7 @@
     </row>
     <row r="3" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="12">
         <v>11.963570000000001</v>
@@ -27489,13 +27488,13 @@
         <v>11</v>
       </c>
       <c r="F3" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>76</v>
       </c>
       <c r="I3" s="11">
         <v>1000000</v>
@@ -27505,7 +27504,7 @@
         <v>2021</v>
       </c>
       <c r="L3" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M3" s="15"/>
       <c r="N3" s="15"/>
@@ -27524,7 +27523,7 @@
     </row>
     <row r="4" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" s="12">
         <v>12.269209999999999</v>
@@ -27539,23 +27538,23 @@
         <v>11</v>
       </c>
       <c r="F4" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>78</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>79</v>
       </c>
       <c r="J4" s="11"/>
       <c r="K4" s="11">
         <v>2021</v>
       </c>
       <c r="L4" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M4" s="15"/>
       <c r="N4" s="15"/>
@@ -27589,25 +27588,25 @@
         <v>11</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I5" s="11">
         <v>1600000</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K5" s="11">
         <v>2021</v>
       </c>
       <c r="L5" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M5" s="15"/>
       <c r="N5" s="15"/>
@@ -27641,13 +27640,13 @@
         <v>11</v>
       </c>
       <c r="F6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="G6" s="11" t="s">
+      <c r="H6" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>83</v>
       </c>
       <c r="I6" s="11"/>
       <c r="J6" s="11"/>
@@ -27655,7 +27654,7 @@
         <v>2021</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M6" s="15"/>
       <c r="N6" s="15"/>
@@ -27689,25 +27688,25 @@
         <v>11</v>
       </c>
       <c r="F7" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H7" s="11" t="s">
         <v>84</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>85</v>
       </c>
       <c r="I7" s="11">
         <v>1500000</v>
       </c>
       <c r="J7" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K7" s="11">
         <v>2021</v>
       </c>
       <c r="L7" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M7" s="15"/>
       <c r="N7" s="15"/>
@@ -27741,21 +27740,21 @@
         <v>11</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G8" s="11"/>
       <c r="H8" s="11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J8" s="11"/>
       <c r="K8" s="11">
         <v>2021</v>
       </c>
       <c r="L8" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
@@ -27789,25 +27788,25 @@
         <v>11</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="I9" s="11">
         <v>1300000</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K9" s="11">
         <v>2021</v>
       </c>
       <c r="L9" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
@@ -27841,23 +27840,23 @@
         <v>11</v>
       </c>
       <c r="F10" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H10" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>90</v>
-      </c>
       <c r="I10" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J10" s="11"/>
       <c r="K10" s="11">
         <v>2021</v>
       </c>
       <c r="L10" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M10" s="15"/>
       <c r="N10" s="15"/>
@@ -27891,23 +27890,23 @@
         <v>11</v>
       </c>
       <c r="F11" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="H11" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>92</v>
-      </c>
       <c r="I11" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="J11" s="11"/>
       <c r="K11" s="11">
         <v>2021</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M11" s="15"/>
       <c r="N11" s="15"/>
@@ -27926,7 +27925,7 @@
     </row>
     <row r="12" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="12">
         <v>12.74245</v>
@@ -27941,25 +27940,25 @@
         <v>11</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I12" s="11">
         <v>1000000</v>
       </c>
       <c r="J12" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K12" s="11">
         <v>2021</v>
       </c>
       <c r="L12" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M12" s="15"/>
       <c r="N12" s="15"/>
@@ -27978,7 +27977,7 @@
     </row>
     <row r="13" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="12">
         <v>9.7164300000000008</v>
@@ -27993,13 +27992,13 @@
         <v>11</v>
       </c>
       <c r="F13" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="G13" s="11" t="s">
-        <v>75</v>
-      </c>
       <c r="H13" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I13" s="11">
         <v>1000000</v>
@@ -28009,7 +28008,7 @@
         <v>2021</v>
       </c>
       <c r="L13" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M13" s="15"/>
       <c r="N13" s="15"/>
@@ -28043,25 +28042,25 @@
         <v>11</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I14" s="11">
         <v>1300000</v>
       </c>
       <c r="J14" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K14" s="11">
         <v>2021</v>
       </c>
       <c r="L14" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M14" s="15"/>
       <c r="N14" s="15"/>
@@ -28096,10 +28095,10 @@
       </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>98</v>
       </c>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
@@ -28107,7 +28106,7 @@
         <v>2021</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M15" s="15"/>
       <c r="N15" s="15"/>
@@ -28141,13 +28140,13 @@
         <v>18</v>
       </c>
       <c r="F16" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" s="11" t="s">
         <v>99</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>100</v>
       </c>
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
@@ -28155,7 +28154,7 @@
         <v>2021</v>
       </c>
       <c r="L16" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M16" s="15"/>
       <c r="N16" s="15"/>
@@ -28189,13 +28188,13 @@
         <v>18</v>
       </c>
       <c r="F17" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>102</v>
       </c>
       <c r="I17" s="11"/>
       <c r="J17" s="11"/>
@@ -28203,7 +28202,7 @@
         <v>2021</v>
       </c>
       <c r="L17" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M17" s="15"/>
       <c r="N17" s="15"/>
@@ -28222,7 +28221,7 @@
     </row>
     <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B18" s="12">
         <v>11.924099999999999</v>
@@ -28237,25 +28236,25 @@
         <v>9</v>
       </c>
       <c r="F18" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G18" s="11" t="s">
+      <c r="H18" s="11" t="s">
         <v>104</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>105</v>
       </c>
       <c r="I18" s="11">
         <v>600</v>
       </c>
       <c r="J18" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K18" s="11">
         <v>2021</v>
       </c>
       <c r="L18" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M18" s="15"/>
       <c r="N18" s="15"/>
@@ -28289,25 +28288,25 @@
         <v>9</v>
       </c>
       <c r="F19" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H19" s="11" t="s">
         <v>107</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>108</v>
       </c>
       <c r="I19" s="11">
         <v>180000</v>
       </c>
       <c r="J19" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K19" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L19" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="L19" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="M19" s="15"/>
       <c r="N19" s="15"/>
@@ -28326,7 +28325,7 @@
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="12">
         <v>11.30925</v>
@@ -28341,25 +28340,25 @@
         <v>9</v>
       </c>
       <c r="F20" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H20" s="11" t="s">
         <v>111</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H20" s="11" t="s">
-        <v>112</v>
       </c>
       <c r="I20" s="11">
         <v>130000</v>
       </c>
       <c r="J20" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K20" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L20" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="L20" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="M20" s="15"/>
       <c r="N20" s="15"/>
@@ -28393,25 +28392,25 @@
         <v>9</v>
       </c>
       <c r="F21" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H21" s="11" t="s">
         <v>113</v>
-      </c>
-      <c r="G21" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H21" s="11" t="s">
-        <v>114</v>
       </c>
       <c r="I21" s="11">
         <v>421000</v>
       </c>
       <c r="J21" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K21" s="11">
         <v>2021</v>
       </c>
       <c r="L21" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M21" s="15"/>
       <c r="N21" s="15"/>
@@ -28445,25 +28444,25 @@
         <v>9</v>
       </c>
       <c r="F22" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H22" s="11" t="s">
         <v>115</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H22" s="11" t="s">
-        <v>116</v>
       </c>
       <c r="I22" s="11">
         <v>730000</v>
       </c>
       <c r="J22" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K22" s="11">
         <v>2022</v>
       </c>
       <c r="L22" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M22" s="15"/>
       <c r="N22" s="15"/>
@@ -28497,25 +28496,25 @@
         <v>9</v>
       </c>
       <c r="F23" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>119</v>
       </c>
       <c r="I23" s="11">
         <v>110000</v>
       </c>
       <c r="J23" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K23" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L23" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="L23" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="M23" s="15"/>
       <c r="N23" s="15"/>
@@ -28549,25 +28548,25 @@
         <v>9</v>
       </c>
       <c r="F24" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H24" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="G24" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>121</v>
       </c>
       <c r="I24" s="11">
         <v>93000</v>
       </c>
       <c r="J24" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K24" s="11">
         <v>2021</v>
       </c>
       <c r="L24" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M24" s="15"/>
       <c r="N24" s="15"/>
@@ -28601,25 +28600,25 @@
         <v>9</v>
       </c>
       <c r="F25" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H25" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>123</v>
       </c>
       <c r="I25" s="11">
         <v>150000</v>
       </c>
       <c r="J25" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K25" s="11">
         <v>2021</v>
       </c>
       <c r="L25" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M25" s="15"/>
       <c r="N25" s="15"/>
@@ -28653,25 +28652,25 @@
         <v>9</v>
       </c>
       <c r="F26" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H26" s="11" t="s">
         <v>124</v>
-      </c>
-      <c r="G26" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>125</v>
       </c>
       <c r="I26" s="11">
         <v>100000</v>
       </c>
       <c r="J26" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K26" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L26" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="L26" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="M26" s="15"/>
       <c r="N26" s="15"/>
@@ -28705,25 +28704,25 @@
         <v>9</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="I27" s="11">
         <v>540000</v>
       </c>
       <c r="J27" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K27" s="11">
         <v>2021</v>
       </c>
       <c r="L27" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M27" s="15"/>
       <c r="N27" s="15"/>
@@ -28757,25 +28756,25 @@
         <v>9</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G28" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="H28" s="11" t="s">
         <v>127</v>
-      </c>
-      <c r="H28" s="11" t="s">
-        <v>128</v>
       </c>
       <c r="I28" s="11">
         <v>160000</v>
       </c>
       <c r="J28" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K28" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="L28" s="11" t="s">
         <v>109</v>
-      </c>
-      <c r="L28" s="11" t="s">
-        <v>110</v>
       </c>
       <c r="M28" s="15"/>
       <c r="N28" s="15"/>
@@ -28809,25 +28808,25 @@
         <v>9</v>
       </c>
       <c r="F29" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H29" s="11" t="s">
         <v>129</v>
-      </c>
-      <c r="G29" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H29" s="11" t="s">
-        <v>130</v>
       </c>
       <c r="I29" s="11">
         <v>174900</v>
       </c>
       <c r="J29" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K29" s="11">
         <v>2021</v>
       </c>
       <c r="L29" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M29" s="15"/>
       <c r="N29" s="15"/>
@@ -28861,25 +28860,25 @@
         <v>9</v>
       </c>
       <c r="F30" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H30" s="11" t="s">
         <v>131</v>
-      </c>
-      <c r="G30" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H30" s="11" t="s">
-        <v>132</v>
       </c>
       <c r="I30" s="11">
         <v>93400</v>
       </c>
       <c r="J30" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K30" s="11">
         <v>2021</v>
       </c>
       <c r="L30" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M30" s="15"/>
       <c r="N30" s="15"/>
@@ -28898,7 +28897,7 @@
     </row>
     <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B31" s="12">
         <v>13.80006</v>
@@ -28913,25 +28912,25 @@
         <v>9</v>
       </c>
       <c r="F31" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G31" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="G31" s="11" t="s">
-        <v>104</v>
-      </c>
       <c r="H31" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I31" s="11">
         <v>612</v>
       </c>
       <c r="J31" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="K31" s="11">
         <v>2021</v>
       </c>
       <c r="L31" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M31" s="15"/>
       <c r="N31" s="15"/>
@@ -28950,7 +28949,7 @@
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B32" s="12">
         <v>12.63189</v>
@@ -28965,25 +28964,25 @@
         <v>9</v>
       </c>
       <c r="F32" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H32" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="G32" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H32" s="11" t="s">
-        <v>135</v>
       </c>
       <c r="I32" s="11">
         <v>150000</v>
       </c>
       <c r="J32" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K32" s="11">
         <v>2021</v>
       </c>
       <c r="L32" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M32" s="15"/>
       <c r="N32" s="15"/>
@@ -29002,7 +29001,7 @@
     </row>
     <row r="33" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B33" s="12">
         <v>11.556369999999999</v>
@@ -29017,25 +29016,25 @@
         <v>9</v>
       </c>
       <c r="F33" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I33" s="11">
         <v>153333.33333333331</v>
       </c>
       <c r="J33" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K33" s="11">
         <v>2021</v>
       </c>
       <c r="L33" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M33" s="15"/>
       <c r="N33" s="15"/>
@@ -29054,7 +29053,7 @@
     </row>
     <row r="34" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B34" s="12">
         <v>12.08798</v>
@@ -29069,25 +29068,25 @@
         <v>9</v>
       </c>
       <c r="F34" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I34" s="11">
         <v>120000</v>
       </c>
       <c r="J34" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K34" s="11">
         <v>2021</v>
       </c>
       <c r="L34" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M34" s="15"/>
       <c r="N34" s="15"/>
@@ -29106,7 +29105,7 @@
     </row>
     <row r="35" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="12">
         <v>11.428890000000001</v>
@@ -29121,25 +29120,25 @@
         <v>9</v>
       </c>
       <c r="F35" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H35" s="11" t="s">
         <v>138</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H35" s="11" t="s">
-        <v>139</v>
       </c>
       <c r="I35" s="11">
         <v>222000</v>
       </c>
       <c r="J35" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K35" s="11">
         <v>2021</v>
       </c>
       <c r="L35" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M35" s="15"/>
       <c r="N35" s="15"/>
@@ -29158,7 +29157,7 @@
     </row>
     <row r="36" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
-        <v>38</v>
+        <v>167</v>
       </c>
       <c r="B36" s="12">
         <v>10.943759999999999</v>
@@ -29173,25 +29172,25 @@
         <v>9</v>
       </c>
       <c r="F36" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I36" s="11">
         <v>203125</v>
       </c>
       <c r="J36" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K36" s="11">
         <v>2021</v>
       </c>
       <c r="L36" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M36" s="15"/>
       <c r="N36" s="15"/>
@@ -29225,25 +29224,25 @@
         <v>9</v>
       </c>
       <c r="F37" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="G37" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="G37" s="11" t="s">
+      <c r="H37" s="11" t="s">
         <v>142</v>
-      </c>
-      <c r="H37" s="11" t="s">
-        <v>143</v>
       </c>
       <c r="I37" s="11">
         <v>195000</v>
       </c>
       <c r="J37" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K37" s="11">
         <v>2021</v>
       </c>
       <c r="L37" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M37" s="15"/>
       <c r="N37" s="15"/>
@@ -29277,25 +29276,25 @@
         <v>9</v>
       </c>
       <c r="F38" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H38" s="11" t="s">
         <v>144</v>
-      </c>
-      <c r="G38" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="H38" s="11" t="s">
-        <v>145</v>
       </c>
       <c r="I38" s="11">
         <v>380000</v>
       </c>
       <c r="J38" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K38" s="11">
         <v>2021</v>
       </c>
       <c r="L38" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M38" s="15"/>
       <c r="N38" s="15"/>
@@ -29314,7 +29313,7 @@
     </row>
     <row r="39" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B39" s="12">
         <v>9.7325099999999996</v>
@@ -29329,25 +29328,25 @@
         <v>9</v>
       </c>
       <c r="F39" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I39" s="11">
         <v>120000</v>
       </c>
       <c r="J39" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K39" s="11">
         <v>2021</v>
       </c>
       <c r="L39" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M39" s="15"/>
       <c r="N39" s="15"/>
@@ -29368,18 +29367,18 @@
     <row r="41" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="42" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B42" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="16" t="s">
         <v>58</v>
-      </c>
-      <c r="C42" s="16" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="43" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B43" s="4">
         <v>12.053710000000001</v>
@@ -29390,7 +29389,7 @@
     </row>
     <row r="44" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="4">
         <v>11.69642</v>
@@ -29401,7 +29400,7 @@
     </row>
     <row r="45" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B45" s="4">
         <v>10.748810000000001</v>
@@ -29412,7 +29411,7 @@
     </row>
     <row r="46" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B46" s="4">
         <v>9.0727600000000006</v>
@@ -29434,7 +29433,7 @@
     </row>
     <row r="48" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B48" s="4">
         <v>8.3271999999999995</v>
@@ -29445,7 +29444,7 @@
     </row>
     <row r="49" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B49" s="4">
         <v>8.6266800000000003</v>
@@ -29456,7 +29455,7 @@
     </row>
     <row r="50" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B50" s="4">
         <v>8.4164499999999993</v>
@@ -29467,7 +29466,7 @@
     </row>
     <row r="51" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B51" s="4">
         <v>9.1895100000000003</v>
@@ -29478,7 +29477,7 @@
     </row>
     <row r="52" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B52" s="4">
         <v>7.6868600000000002</v>
@@ -29489,7 +29488,7 @@
     </row>
     <row r="53" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B53" s="4">
         <v>8.9330499999999997</v>
@@ -29500,7 +29499,7 @@
     </row>
     <row r="54" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B54" s="4">
         <v>10.991619999999999</v>
@@ -29511,7 +29510,7 @@
     </row>
     <row r="55" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B55" s="4">
         <v>11.338749999999999</v>
@@ -29522,7 +29521,7 @@
     </row>
     <row r="56" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B56" s="4">
         <v>13.77692</v>
@@ -29533,7 +29532,7 @@
     </row>
     <row r="57" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B57" s="4">
         <v>12.31551</v>
@@ -29556,18 +29555,18 @@
     <row r="59" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="60" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B60" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C60" s="19" t="s">
         <v>58</v>
-      </c>
-      <c r="C60" s="19" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B61" s="2">
         <v>12.274480000000001</v>
@@ -29579,18 +29578,18 @@
     <row r="62" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="63" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B63" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C63" s="19" t="s">
         <v>58</v>
-      </c>
-      <c r="C63" s="19" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B64" s="4">
         <v>10.64</v>
@@ -29602,25 +29601,25 @@
     <row r="65" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="66" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B66" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="B66" s="19" t="s">
+      <c r="C66" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="D66" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="E66" s="20" t="s">
         <v>164</v>
       </c>
-      <c r="C66" s="19" t="s">
-        <v>58</v>
-      </c>
-      <c r="D66" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="E66" s="20" t="s">
+      <c r="F66" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="F66" s="20" t="s">
+      <c r="G66" s="9" t="s">
         <v>166</v>
-      </c>
-      <c r="G66" s="9" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -29696,7 +29695,7 @@
       <c r="A70" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B70" s="27">
+      <c r="B70">
         <v>23</v>
       </c>
       <c r="C70" s="2">
@@ -29740,7 +29739,7 @@
     </row>
     <row r="72" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B72" s="1">
         <v>34</v>
@@ -29763,7 +29762,7 @@
     </row>
     <row r="73" spans="1:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B73" s="1">
         <v>42</v>
